--- a/ES2N-Requisitos Funcionais IAgora V2.0.xlsx
+++ b/ES2N-Requisitos Funcionais IAgora V2.0.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="31">
   <si>
     <t xml:space="preserve">LISTA DE REQUISITOS FUNCIONAIS </t>
   </si>
@@ -104,7 +104,44 @@
     <t xml:space="preserve">Gerenciar cadastro de documentos</t>
   </si>
   <si>
-    <t xml:space="preserve">Esse requisito permite que o usuário gerencie o cadastro de nome do documento, setor/colaborador responsável, data de emissão e de validade.</t>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val=""/>
+        <family val="1"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Esse requisito permite que o usuário gerencie o cadastro de</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val=""/>
+        <family val="1"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <rFont val="Arial"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">Área do documento, versão, periodicidade, status (vencido, vence em breve, vencido, etc), e-mail do responsável</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val=""/>
+        <family val="1"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">Alta</t>
@@ -149,7 +186,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">Deve</t>
+      <t xml:space="preserve">Pode</t>
     </r>
     <r>
       <rPr>
@@ -183,6 +220,24 @@
   <si>
     <t xml:space="preserve">Esse requisito envia alertas por e-mail, pelos dashboard ou webhooks.</t>
   </si>
+  <si>
+    <t xml:space="preserve">RF05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gerenciar cadastro de responsáveis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Esse requisito permite que o usuário gerencie o cadastro de nome, setor e e-mail dos colaboradores cadastrados para quem os avisos serão enviados</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RF06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fazer login</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Esse requisito permite que o usuário administrador se conecte com o sistema para usá-lo</t>
+  </si>
 </sst>
 </file>
 
@@ -191,7 +246,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="13">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -244,6 +299,25 @@
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val=""/>
+      <family val="1"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val=""/>
+      <family val="1"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <name val="Arial"/>
+      <family val="1"/>
     </font>
     <font>
       <sz val="18"/>
@@ -309,52 +383,56 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="justify" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="justify" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -610,10 +688,10 @@
   <dimension ref="A1:E54"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="32.34"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="25.56"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="32.34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="25.56"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="78"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="20.11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="20.11"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="46.22"/>
   </cols>
   <sheetData>
@@ -639,7 +717,7 @@
       <c r="B4" s="3"/>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
+      <c r="A6" s="1" t="s">
         <v>3</v>
       </c>
     </row>
@@ -684,13 +762,13 @@
       <c r="B11" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="C11" s="7" t="s">
+      <c r="C11" s="10" t="s">
         <v>16</v>
       </c>
       <c r="D11" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="E11" s="10" t="s">
+      <c r="E11" s="11" t="s">
         <v>17</v>
       </c>
     </row>
@@ -701,7 +779,7 @@
       <c r="B12" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="C12" s="7" t="s">
+      <c r="C12" s="10" t="s">
         <v>20</v>
       </c>
       <c r="D12" s="5" t="s">
@@ -716,26 +794,41 @@
       <c r="B13" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="C13" s="7" t="s">
+      <c r="C13" s="10" t="s">
         <v>24</v>
       </c>
       <c r="D13" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="E13" s="4"/>
-    </row>
-    <row r="14" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="5"/>
-      <c r="B14" s="5"/>
-      <c r="C14" s="4"/>
-      <c r="D14" s="5"/>
-      <c r="E14" s="4"/>
-    </row>
-    <row r="15" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="5"/>
-      <c r="B15" s="5"/>
-      <c r="C15" s="4"/>
-      <c r="D15" s="5"/>
+    </row>
+    <row r="14" customFormat="false" ht="55.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="E14" s="11"/>
+    </row>
+    <row r="15" customFormat="false" ht="37.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>21</v>
+      </c>
       <c r="E15" s="4"/>
     </row>
     <row r="16" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -760,7 +853,7 @@
       <c r="E18" s="4"/>
     </row>
     <row r="19" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="11"/>
+      <c r="A19" s="12"/>
       <c r="B19" s="5"/>
       <c r="C19" s="4"/>
       <c r="D19" s="5"/>
